--- a/financial/src/main/resources/template/salary.xlsx
+++ b/financial/src/main/resources/template/salary.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="48">
   <si>
     <t>工资表--1月</t>
   </si>
@@ -182,6 +182,10 @@
      2.工资模板导入时只支持第一个sheet数据导入，导入某月份的工资表时，需要将该月份工资表的sheet移动到第一个sheet位置</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
+  <si>
+    <t>应发工资</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -207,11 +211,13 @@
       <b/>
       <sz val="10"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -223,6 +229,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -231,6 +238,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -329,14 +337,14 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -699,64 +707,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:33" ht="47" customHeight="1">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
-      <c r="O1" s="14"/>
-      <c r="P1" s="14"/>
-      <c r="Q1" s="14"/>
-      <c r="R1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:33" s="1" customFormat="1" ht="21" customHeight="1">
-      <c r="A2" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="15"/>
-      <c r="O2" s="15"/>
-      <c r="P2" s="15"/>
-      <c r="Q2" s="15"/>
-      <c r="R2" s="15"/>
-      <c r="S2" s="15"/>
-      <c r="T2" s="15"/>
-      <c r="U2" s="15"/>
-      <c r="V2" s="15"/>
-      <c r="W2" s="15"/>
-      <c r="X2" s="15"/>
-      <c r="Y2" s="15"/>
-      <c r="Z2" s="15"/>
-      <c r="AA2" s="15"/>
-      <c r="AB2" s="15"/>
-      <c r="AC2" s="15"/>
-      <c r="AD2" s="15"/>
-      <c r="AE2" s="15"/>
-      <c r="AF2" s="15"/>
-      <c r="AG2" s="15"/>
+      <c r="A2" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16"/>
+      <c r="N2" s="16"/>
+      <c r="O2" s="16"/>
+      <c r="P2" s="16"/>
+      <c r="Q2" s="16"/>
+      <c r="R2" s="16"/>
+      <c r="S2" s="16"/>
+      <c r="T2" s="16"/>
+      <c r="U2" s="16"/>
+      <c r="V2" s="16"/>
+      <c r="W2" s="16"/>
+      <c r="X2" s="16"/>
+      <c r="Y2" s="16"/>
+      <c r="Z2" s="16"/>
+      <c r="AA2" s="16"/>
+      <c r="AB2" s="16"/>
+      <c r="AC2" s="16"/>
+      <c r="AD2" s="16"/>
+      <c r="AE2" s="16"/>
+      <c r="AF2" s="16"/>
+      <c r="AG2" s="16"/>
     </row>
     <row r="3" spans="1:33" ht="13">
       <c r="A3" s="3" t="s">
@@ -1401,70 +1409,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" ht="47" customHeight="1">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
-      <c r="O1" s="14"/>
-      <c r="P1" s="14"/>
-      <c r="Q1" s="14"/>
-      <c r="R1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15"/>
     </row>
     <row r="2" spans="1:40" s="1" customFormat="1" ht="21" customHeight="1">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="15"/>
-      <c r="O2" s="15"/>
-      <c r="P2" s="15"/>
-      <c r="Q2" s="15"/>
-      <c r="R2" s="15"/>
-      <c r="S2" s="15"/>
-      <c r="T2" s="15"/>
-      <c r="U2" s="15"/>
-      <c r="V2" s="15"/>
-      <c r="W2" s="15"/>
-      <c r="X2" s="15"/>
-      <c r="Y2" s="15"/>
-      <c r="Z2" s="15"/>
-      <c r="AA2" s="15"/>
-      <c r="AB2" s="15"/>
-      <c r="AC2" s="15"/>
-      <c r="AD2" s="15"/>
-      <c r="AE2" s="15"/>
-      <c r="AF2" s="15"/>
-      <c r="AG2" s="15"/>
-      <c r="AH2" s="15"/>
-      <c r="AI2" s="15"/>
-      <c r="AJ2" s="15"/>
-      <c r="AK2" s="15"/>
-      <c r="AL2" s="15"/>
-      <c r="AM2" s="15"/>
-      <c r="AN2" s="15"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16"/>
+      <c r="N2" s="16"/>
+      <c r="O2" s="16"/>
+      <c r="P2" s="16"/>
+      <c r="Q2" s="16"/>
+      <c r="R2" s="16"/>
+      <c r="S2" s="16"/>
+      <c r="T2" s="16"/>
+      <c r="U2" s="16"/>
+      <c r="V2" s="16"/>
+      <c r="W2" s="16"/>
+      <c r="X2" s="16"/>
+      <c r="Y2" s="16"/>
+      <c r="Z2" s="16"/>
+      <c r="AA2" s="16"/>
+      <c r="AB2" s="16"/>
+      <c r="AC2" s="16"/>
+      <c r="AD2" s="16"/>
+      <c r="AE2" s="16"/>
+      <c r="AF2" s="16"/>
+      <c r="AG2" s="16"/>
+      <c r="AH2" s="16"/>
+      <c r="AI2" s="16"/>
+      <c r="AJ2" s="16"/>
+      <c r="AK2" s="16"/>
+      <c r="AL2" s="16"/>
+      <c r="AM2" s="16"/>
+      <c r="AN2" s="16"/>
     </row>
     <row r="3" spans="1:40" ht="13">
       <c r="A3" s="3" t="s">
@@ -2073,7 +2081,6 @@
       <c r="AG16" s="6"/>
     </row>
   </sheetData>
-  <sheetCalcPr fullCalcOnLoad="1"/>
   <mergeCells count="2">
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="A2:AN2"/>
@@ -2109,70 +2116,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" ht="47" customHeight="1">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
-      <c r="O1" s="14"/>
-      <c r="P1" s="14"/>
-      <c r="Q1" s="14"/>
-      <c r="R1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15"/>
     </row>
     <row r="2" spans="1:40" s="1" customFormat="1" ht="21" customHeight="1">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="15"/>
-      <c r="O2" s="15"/>
-      <c r="P2" s="15"/>
-      <c r="Q2" s="15"/>
-      <c r="R2" s="15"/>
-      <c r="S2" s="15"/>
-      <c r="T2" s="15"/>
-      <c r="U2" s="15"/>
-      <c r="V2" s="15"/>
-      <c r="W2" s="15"/>
-      <c r="X2" s="15"/>
-      <c r="Y2" s="15"/>
-      <c r="Z2" s="15"/>
-      <c r="AA2" s="15"/>
-      <c r="AB2" s="15"/>
-      <c r="AC2" s="15"/>
-      <c r="AD2" s="15"/>
-      <c r="AE2" s="15"/>
-      <c r="AF2" s="15"/>
-      <c r="AG2" s="15"/>
-      <c r="AH2" s="15"/>
-      <c r="AI2" s="15"/>
-      <c r="AJ2" s="15"/>
-      <c r="AK2" s="15"/>
-      <c r="AL2" s="15"/>
-      <c r="AM2" s="15"/>
-      <c r="AN2" s="15"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16"/>
+      <c r="N2" s="16"/>
+      <c r="O2" s="16"/>
+      <c r="P2" s="16"/>
+      <c r="Q2" s="16"/>
+      <c r="R2" s="16"/>
+      <c r="S2" s="16"/>
+      <c r="T2" s="16"/>
+      <c r="U2" s="16"/>
+      <c r="V2" s="16"/>
+      <c r="W2" s="16"/>
+      <c r="X2" s="16"/>
+      <c r="Y2" s="16"/>
+      <c r="Z2" s="16"/>
+      <c r="AA2" s="16"/>
+      <c r="AB2" s="16"/>
+      <c r="AC2" s="16"/>
+      <c r="AD2" s="16"/>
+      <c r="AE2" s="16"/>
+      <c r="AF2" s="16"/>
+      <c r="AG2" s="16"/>
+      <c r="AH2" s="16"/>
+      <c r="AI2" s="16"/>
+      <c r="AJ2" s="16"/>
+      <c r="AK2" s="16"/>
+      <c r="AL2" s="16"/>
+      <c r="AM2" s="16"/>
+      <c r="AN2" s="16"/>
     </row>
     <row r="3" spans="1:40" ht="13">
       <c r="A3" s="3" t="s">
@@ -2781,7 +2788,6 @@
       <c r="AG16" s="6"/>
     </row>
   </sheetData>
-  <sheetCalcPr fullCalcOnLoad="1"/>
   <mergeCells count="2">
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="A2:AN2"/>
@@ -2816,70 +2822,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" ht="47" customHeight="1">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
-      <c r="O1" s="14"/>
-      <c r="P1" s="14"/>
-      <c r="Q1" s="14"/>
-      <c r="R1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15"/>
     </row>
     <row r="2" spans="1:40" s="1" customFormat="1" ht="21" customHeight="1">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="15"/>
-      <c r="O2" s="15"/>
-      <c r="P2" s="15"/>
-      <c r="Q2" s="15"/>
-      <c r="R2" s="15"/>
-      <c r="S2" s="15"/>
-      <c r="T2" s="15"/>
-      <c r="U2" s="15"/>
-      <c r="V2" s="15"/>
-      <c r="W2" s="15"/>
-      <c r="X2" s="15"/>
-      <c r="Y2" s="15"/>
-      <c r="Z2" s="15"/>
-      <c r="AA2" s="15"/>
-      <c r="AB2" s="15"/>
-      <c r="AC2" s="15"/>
-      <c r="AD2" s="15"/>
-      <c r="AE2" s="15"/>
-      <c r="AF2" s="15"/>
-      <c r="AG2" s="15"/>
-      <c r="AH2" s="15"/>
-      <c r="AI2" s="15"/>
-      <c r="AJ2" s="15"/>
-      <c r="AK2" s="15"/>
-      <c r="AL2" s="15"/>
-      <c r="AM2" s="15"/>
-      <c r="AN2" s="15"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16"/>
+      <c r="N2" s="16"/>
+      <c r="O2" s="16"/>
+      <c r="P2" s="16"/>
+      <c r="Q2" s="16"/>
+      <c r="R2" s="16"/>
+      <c r="S2" s="16"/>
+      <c r="T2" s="16"/>
+      <c r="U2" s="16"/>
+      <c r="V2" s="16"/>
+      <c r="W2" s="16"/>
+      <c r="X2" s="16"/>
+      <c r="Y2" s="16"/>
+      <c r="Z2" s="16"/>
+      <c r="AA2" s="16"/>
+      <c r="AB2" s="16"/>
+      <c r="AC2" s="16"/>
+      <c r="AD2" s="16"/>
+      <c r="AE2" s="16"/>
+      <c r="AF2" s="16"/>
+      <c r="AG2" s="16"/>
+      <c r="AH2" s="16"/>
+      <c r="AI2" s="16"/>
+      <c r="AJ2" s="16"/>
+      <c r="AK2" s="16"/>
+      <c r="AL2" s="16"/>
+      <c r="AM2" s="16"/>
+      <c r="AN2" s="16"/>
     </row>
     <row r="3" spans="1:40" ht="13">
       <c r="A3" s="3" t="s">
@@ -2922,7 +2928,7 @@
         <v>13</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="O3" s="3" t="s">
         <v>15</v>
@@ -3536,7 +3542,6 @@
       <c r="O34" s="12"/>
     </row>
   </sheetData>
-  <sheetCalcPr fullCalcOnLoad="1"/>
   <mergeCells count="2">
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="A2:AN2"/>
@@ -3579,63 +3584,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:33" ht="47" customHeight="1">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
-      <c r="O1" s="14"/>
-      <c r="P1" s="14"/>
-      <c r="Q1" s="14"/>
-      <c r="R1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15"/>
     </row>
     <row r="2" spans="1:33" s="1" customFormat="1" ht="21" customHeight="1">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="15"/>
-      <c r="O2" s="15"/>
-      <c r="P2" s="15"/>
-      <c r="Q2" s="15"/>
-      <c r="R2" s="15"/>
-      <c r="S2" s="15"/>
-      <c r="T2" s="15"/>
-      <c r="U2" s="15"/>
-      <c r="V2" s="15"/>
-      <c r="W2" s="15"/>
-      <c r="X2" s="15"/>
-      <c r="Y2" s="15"/>
-      <c r="Z2" s="15"/>
-      <c r="AA2" s="15"/>
-      <c r="AB2" s="15"/>
-      <c r="AC2" s="15"/>
-      <c r="AD2" s="15"/>
-      <c r="AE2" s="15"/>
-      <c r="AF2" s="15"/>
-      <c r="AG2" s="15"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16"/>
+      <c r="N2" s="16"/>
+      <c r="O2" s="16"/>
+      <c r="P2" s="16"/>
+      <c r="Q2" s="16"/>
+      <c r="R2" s="16"/>
+      <c r="S2" s="16"/>
+      <c r="T2" s="16"/>
+      <c r="U2" s="16"/>
+      <c r="V2" s="16"/>
+      <c r="W2" s="16"/>
+      <c r="X2" s="16"/>
+      <c r="Y2" s="16"/>
+      <c r="Z2" s="16"/>
+      <c r="AA2" s="16"/>
+      <c r="AB2" s="16"/>
+      <c r="AC2" s="16"/>
+      <c r="AD2" s="16"/>
+      <c r="AE2" s="16"/>
+      <c r="AF2" s="16"/>
+      <c r="AG2" s="16"/>
     </row>
     <row r="3" spans="1:33" ht="13">
       <c r="A3" s="3" t="s">
@@ -4244,7 +4249,6 @@
       <c r="AG16" s="6"/>
     </row>
   </sheetData>
-  <sheetCalcPr fullCalcOnLoad="1"/>
   <mergeCells count="2">
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="A2:AG2"/>
@@ -4287,70 +4291,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" ht="47" customHeight="1">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
-      <c r="O1" s="14"/>
-      <c r="P1" s="14"/>
-      <c r="Q1" s="14"/>
-      <c r="R1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15"/>
     </row>
     <row r="2" spans="1:40" s="1" customFormat="1" ht="21" customHeight="1">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="15"/>
-      <c r="O2" s="15"/>
-      <c r="P2" s="15"/>
-      <c r="Q2" s="15"/>
-      <c r="R2" s="15"/>
-      <c r="S2" s="15"/>
-      <c r="T2" s="15"/>
-      <c r="U2" s="15"/>
-      <c r="V2" s="15"/>
-      <c r="W2" s="15"/>
-      <c r="X2" s="15"/>
-      <c r="Y2" s="15"/>
-      <c r="Z2" s="15"/>
-      <c r="AA2" s="15"/>
-      <c r="AB2" s="15"/>
-      <c r="AC2" s="15"/>
-      <c r="AD2" s="15"/>
-      <c r="AE2" s="15"/>
-      <c r="AF2" s="15"/>
-      <c r="AG2" s="15"/>
-      <c r="AH2" s="15"/>
-      <c r="AI2" s="15"/>
-      <c r="AJ2" s="15"/>
-      <c r="AK2" s="15"/>
-      <c r="AL2" s="15"/>
-      <c r="AM2" s="15"/>
-      <c r="AN2" s="15"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16"/>
+      <c r="N2" s="16"/>
+      <c r="O2" s="16"/>
+      <c r="P2" s="16"/>
+      <c r="Q2" s="16"/>
+      <c r="R2" s="16"/>
+      <c r="S2" s="16"/>
+      <c r="T2" s="16"/>
+      <c r="U2" s="16"/>
+      <c r="V2" s="16"/>
+      <c r="W2" s="16"/>
+      <c r="X2" s="16"/>
+      <c r="Y2" s="16"/>
+      <c r="Z2" s="16"/>
+      <c r="AA2" s="16"/>
+      <c r="AB2" s="16"/>
+      <c r="AC2" s="16"/>
+      <c r="AD2" s="16"/>
+      <c r="AE2" s="16"/>
+      <c r="AF2" s="16"/>
+      <c r="AG2" s="16"/>
+      <c r="AH2" s="16"/>
+      <c r="AI2" s="16"/>
+      <c r="AJ2" s="16"/>
+      <c r="AK2" s="16"/>
+      <c r="AL2" s="16"/>
+      <c r="AM2" s="16"/>
+      <c r="AN2" s="16"/>
     </row>
     <row r="3" spans="1:40" ht="13">
       <c r="A3" s="3" t="s">
@@ -4959,7 +4963,6 @@
       <c r="AG16" s="6"/>
     </row>
   </sheetData>
-  <sheetCalcPr fullCalcOnLoad="1"/>
   <mergeCells count="2">
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="A2:AN2"/>
@@ -5002,70 +5005,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" ht="47" customHeight="1">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
-      <c r="O1" s="14"/>
-      <c r="P1" s="14"/>
-      <c r="Q1" s="14"/>
-      <c r="R1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15"/>
     </row>
     <row r="2" spans="1:40" s="1" customFormat="1" ht="21" customHeight="1">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="15"/>
-      <c r="O2" s="15"/>
-      <c r="P2" s="15"/>
-      <c r="Q2" s="15"/>
-      <c r="R2" s="15"/>
-      <c r="S2" s="15"/>
-      <c r="T2" s="15"/>
-      <c r="U2" s="15"/>
-      <c r="V2" s="15"/>
-      <c r="W2" s="15"/>
-      <c r="X2" s="15"/>
-      <c r="Y2" s="15"/>
-      <c r="Z2" s="15"/>
-      <c r="AA2" s="15"/>
-      <c r="AB2" s="15"/>
-      <c r="AC2" s="15"/>
-      <c r="AD2" s="15"/>
-      <c r="AE2" s="15"/>
-      <c r="AF2" s="15"/>
-      <c r="AG2" s="15"/>
-      <c r="AH2" s="15"/>
-      <c r="AI2" s="15"/>
-      <c r="AJ2" s="15"/>
-      <c r="AK2" s="15"/>
-      <c r="AL2" s="15"/>
-      <c r="AM2" s="15"/>
-      <c r="AN2" s="15"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16"/>
+      <c r="N2" s="16"/>
+      <c r="O2" s="16"/>
+      <c r="P2" s="16"/>
+      <c r="Q2" s="16"/>
+      <c r="R2" s="16"/>
+      <c r="S2" s="16"/>
+      <c r="T2" s="16"/>
+      <c r="U2" s="16"/>
+      <c r="V2" s="16"/>
+      <c r="W2" s="16"/>
+      <c r="X2" s="16"/>
+      <c r="Y2" s="16"/>
+      <c r="Z2" s="16"/>
+      <c r="AA2" s="16"/>
+      <c r="AB2" s="16"/>
+      <c r="AC2" s="16"/>
+      <c r="AD2" s="16"/>
+      <c r="AE2" s="16"/>
+      <c r="AF2" s="16"/>
+      <c r="AG2" s="16"/>
+      <c r="AH2" s="16"/>
+      <c r="AI2" s="16"/>
+      <c r="AJ2" s="16"/>
+      <c r="AK2" s="16"/>
+      <c r="AL2" s="16"/>
+      <c r="AM2" s="16"/>
+      <c r="AN2" s="16"/>
     </row>
     <row r="3" spans="1:40" ht="13">
       <c r="A3" s="3" t="s">
@@ -5674,7 +5677,6 @@
       <c r="AG16" s="6"/>
     </row>
   </sheetData>
-  <sheetCalcPr fullCalcOnLoad="1"/>
   <mergeCells count="2">
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="A2:AN2"/>
@@ -5708,70 +5710,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" ht="47" customHeight="1">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
-      <c r="O1" s="14"/>
-      <c r="P1" s="14"/>
-      <c r="Q1" s="14"/>
-      <c r="R1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15"/>
     </row>
     <row r="2" spans="1:40" s="1" customFormat="1" ht="21" customHeight="1">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="15"/>
-      <c r="O2" s="15"/>
-      <c r="P2" s="15"/>
-      <c r="Q2" s="15"/>
-      <c r="R2" s="15"/>
-      <c r="S2" s="15"/>
-      <c r="T2" s="15"/>
-      <c r="U2" s="15"/>
-      <c r="V2" s="15"/>
-      <c r="W2" s="15"/>
-      <c r="X2" s="15"/>
-      <c r="Y2" s="15"/>
-      <c r="Z2" s="15"/>
-      <c r="AA2" s="15"/>
-      <c r="AB2" s="15"/>
-      <c r="AC2" s="15"/>
-      <c r="AD2" s="15"/>
-      <c r="AE2" s="15"/>
-      <c r="AF2" s="15"/>
-      <c r="AG2" s="15"/>
-      <c r="AH2" s="15"/>
-      <c r="AI2" s="15"/>
-      <c r="AJ2" s="15"/>
-      <c r="AK2" s="15"/>
-      <c r="AL2" s="15"/>
-      <c r="AM2" s="15"/>
-      <c r="AN2" s="15"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16"/>
+      <c r="N2" s="16"/>
+      <c r="O2" s="16"/>
+      <c r="P2" s="16"/>
+      <c r="Q2" s="16"/>
+      <c r="R2" s="16"/>
+      <c r="S2" s="16"/>
+      <c r="T2" s="16"/>
+      <c r="U2" s="16"/>
+      <c r="V2" s="16"/>
+      <c r="W2" s="16"/>
+      <c r="X2" s="16"/>
+      <c r="Y2" s="16"/>
+      <c r="Z2" s="16"/>
+      <c r="AA2" s="16"/>
+      <c r="AB2" s="16"/>
+      <c r="AC2" s="16"/>
+      <c r="AD2" s="16"/>
+      <c r="AE2" s="16"/>
+      <c r="AF2" s="16"/>
+      <c r="AG2" s="16"/>
+      <c r="AH2" s="16"/>
+      <c r="AI2" s="16"/>
+      <c r="AJ2" s="16"/>
+      <c r="AK2" s="16"/>
+      <c r="AL2" s="16"/>
+      <c r="AM2" s="16"/>
+      <c r="AN2" s="16"/>
     </row>
     <row r="3" spans="1:40" ht="13">
       <c r="A3" s="3" t="s">
@@ -6380,7 +6382,6 @@
       <c r="AG16" s="6"/>
     </row>
   </sheetData>
-  <sheetCalcPr fullCalcOnLoad="1"/>
   <mergeCells count="2">
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="A2:AN2"/>
@@ -6414,70 +6415,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" ht="47" customHeight="1">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
-      <c r="O1" s="14"/>
-      <c r="P1" s="14"/>
-      <c r="Q1" s="14"/>
-      <c r="R1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15"/>
     </row>
     <row r="2" spans="1:40" s="1" customFormat="1" ht="21" customHeight="1">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="15"/>
-      <c r="O2" s="15"/>
-      <c r="P2" s="15"/>
-      <c r="Q2" s="15"/>
-      <c r="R2" s="15"/>
-      <c r="S2" s="15"/>
-      <c r="T2" s="15"/>
-      <c r="U2" s="15"/>
-      <c r="V2" s="15"/>
-      <c r="W2" s="15"/>
-      <c r="X2" s="15"/>
-      <c r="Y2" s="15"/>
-      <c r="Z2" s="15"/>
-      <c r="AA2" s="15"/>
-      <c r="AB2" s="15"/>
-      <c r="AC2" s="15"/>
-      <c r="AD2" s="15"/>
-      <c r="AE2" s="15"/>
-      <c r="AF2" s="15"/>
-      <c r="AG2" s="15"/>
-      <c r="AH2" s="15"/>
-      <c r="AI2" s="15"/>
-      <c r="AJ2" s="15"/>
-      <c r="AK2" s="15"/>
-      <c r="AL2" s="15"/>
-      <c r="AM2" s="15"/>
-      <c r="AN2" s="15"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16"/>
+      <c r="N2" s="16"/>
+      <c r="O2" s="16"/>
+      <c r="P2" s="16"/>
+      <c r="Q2" s="16"/>
+      <c r="R2" s="16"/>
+      <c r="S2" s="16"/>
+      <c r="T2" s="16"/>
+      <c r="U2" s="16"/>
+      <c r="V2" s="16"/>
+      <c r="W2" s="16"/>
+      <c r="X2" s="16"/>
+      <c r="Y2" s="16"/>
+      <c r="Z2" s="16"/>
+      <c r="AA2" s="16"/>
+      <c r="AB2" s="16"/>
+      <c r="AC2" s="16"/>
+      <c r="AD2" s="16"/>
+      <c r="AE2" s="16"/>
+      <c r="AF2" s="16"/>
+      <c r="AG2" s="16"/>
+      <c r="AH2" s="16"/>
+      <c r="AI2" s="16"/>
+      <c r="AJ2" s="16"/>
+      <c r="AK2" s="16"/>
+      <c r="AL2" s="16"/>
+      <c r="AM2" s="16"/>
+      <c r="AN2" s="16"/>
     </row>
     <row r="3" spans="1:40" ht="13">
       <c r="A3" s="3" t="s">
@@ -7086,7 +7087,6 @@
       <c r="AG16" s="6"/>
     </row>
   </sheetData>
-  <sheetCalcPr fullCalcOnLoad="1"/>
   <mergeCells count="2">
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="A2:AN2"/>
@@ -7123,70 +7123,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" ht="47" customHeight="1">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
-      <c r="O1" s="14"/>
-      <c r="P1" s="14"/>
-      <c r="Q1" s="14"/>
-      <c r="R1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15"/>
     </row>
     <row r="2" spans="1:40" s="1" customFormat="1" ht="21" customHeight="1">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="15"/>
-      <c r="O2" s="15"/>
-      <c r="P2" s="15"/>
-      <c r="Q2" s="15"/>
-      <c r="R2" s="15"/>
-      <c r="S2" s="15"/>
-      <c r="T2" s="15"/>
-      <c r="U2" s="15"/>
-      <c r="V2" s="15"/>
-      <c r="W2" s="15"/>
-      <c r="X2" s="15"/>
-      <c r="Y2" s="15"/>
-      <c r="Z2" s="15"/>
-      <c r="AA2" s="15"/>
-      <c r="AB2" s="15"/>
-      <c r="AC2" s="15"/>
-      <c r="AD2" s="15"/>
-      <c r="AE2" s="15"/>
-      <c r="AF2" s="15"/>
-      <c r="AG2" s="15"/>
-      <c r="AH2" s="15"/>
-      <c r="AI2" s="15"/>
-      <c r="AJ2" s="15"/>
-      <c r="AK2" s="15"/>
-      <c r="AL2" s="15"/>
-      <c r="AM2" s="15"/>
-      <c r="AN2" s="15"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16"/>
+      <c r="N2" s="16"/>
+      <c r="O2" s="16"/>
+      <c r="P2" s="16"/>
+      <c r="Q2" s="16"/>
+      <c r="R2" s="16"/>
+      <c r="S2" s="16"/>
+      <c r="T2" s="16"/>
+      <c r="U2" s="16"/>
+      <c r="V2" s="16"/>
+      <c r="W2" s="16"/>
+      <c r="X2" s="16"/>
+      <c r="Y2" s="16"/>
+      <c r="Z2" s="16"/>
+      <c r="AA2" s="16"/>
+      <c r="AB2" s="16"/>
+      <c r="AC2" s="16"/>
+      <c r="AD2" s="16"/>
+      <c r="AE2" s="16"/>
+      <c r="AF2" s="16"/>
+      <c r="AG2" s="16"/>
+      <c r="AH2" s="16"/>
+      <c r="AI2" s="16"/>
+      <c r="AJ2" s="16"/>
+      <c r="AK2" s="16"/>
+      <c r="AL2" s="16"/>
+      <c r="AM2" s="16"/>
+      <c r="AN2" s="16"/>
     </row>
     <row r="3" spans="1:40" ht="13">
       <c r="A3" s="3" t="s">
@@ -7795,7 +7795,6 @@
       <c r="AG16" s="6"/>
     </row>
   </sheetData>
-  <sheetCalcPr fullCalcOnLoad="1"/>
   <mergeCells count="2">
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="A2:AN2"/>
@@ -7833,70 +7832,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" ht="47" customHeight="1">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
-      <c r="O1" s="14"/>
-      <c r="P1" s="14"/>
-      <c r="Q1" s="14"/>
-      <c r="R1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15"/>
     </row>
     <row r="2" spans="1:40" s="1" customFormat="1" ht="21" customHeight="1">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="15"/>
-      <c r="O2" s="15"/>
-      <c r="P2" s="15"/>
-      <c r="Q2" s="15"/>
-      <c r="R2" s="15"/>
-      <c r="S2" s="15"/>
-      <c r="T2" s="15"/>
-      <c r="U2" s="15"/>
-      <c r="V2" s="15"/>
-      <c r="W2" s="15"/>
-      <c r="X2" s="15"/>
-      <c r="Y2" s="15"/>
-      <c r="Z2" s="15"/>
-      <c r="AA2" s="15"/>
-      <c r="AB2" s="15"/>
-      <c r="AC2" s="15"/>
-      <c r="AD2" s="15"/>
-      <c r="AE2" s="15"/>
-      <c r="AF2" s="15"/>
-      <c r="AG2" s="15"/>
-      <c r="AH2" s="15"/>
-      <c r="AI2" s="15"/>
-      <c r="AJ2" s="15"/>
-      <c r="AK2" s="15"/>
-      <c r="AL2" s="15"/>
-      <c r="AM2" s="15"/>
-      <c r="AN2" s="15"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16"/>
+      <c r="N2" s="16"/>
+      <c r="O2" s="16"/>
+      <c r="P2" s="16"/>
+      <c r="Q2" s="16"/>
+      <c r="R2" s="16"/>
+      <c r="S2" s="16"/>
+      <c r="T2" s="16"/>
+      <c r="U2" s="16"/>
+      <c r="V2" s="16"/>
+      <c r="W2" s="16"/>
+      <c r="X2" s="16"/>
+      <c r="Y2" s="16"/>
+      <c r="Z2" s="16"/>
+      <c r="AA2" s="16"/>
+      <c r="AB2" s="16"/>
+      <c r="AC2" s="16"/>
+      <c r="AD2" s="16"/>
+      <c r="AE2" s="16"/>
+      <c r="AF2" s="16"/>
+      <c r="AG2" s="16"/>
+      <c r="AH2" s="16"/>
+      <c r="AI2" s="16"/>
+      <c r="AJ2" s="16"/>
+      <c r="AK2" s="16"/>
+      <c r="AL2" s="16"/>
+      <c r="AM2" s="16"/>
+      <c r="AN2" s="16"/>
     </row>
     <row r="3" spans="1:40" ht="13">
       <c r="A3" s="3" t="s">
@@ -8505,7 +8504,6 @@
       <c r="AG16" s="6"/>
     </row>
   </sheetData>
-  <sheetCalcPr fullCalcOnLoad="1"/>
   <mergeCells count="2">
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="A2:AN2"/>
@@ -8541,70 +8539,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" ht="47" customHeight="1">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
-      <c r="O1" s="14"/>
-      <c r="P1" s="14"/>
-      <c r="Q1" s="14"/>
-      <c r="R1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15"/>
     </row>
     <row r="2" spans="1:40" s="1" customFormat="1" ht="21" customHeight="1">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="15"/>
-      <c r="O2" s="15"/>
-      <c r="P2" s="15"/>
-      <c r="Q2" s="15"/>
-      <c r="R2" s="15"/>
-      <c r="S2" s="15"/>
-      <c r="T2" s="15"/>
-      <c r="U2" s="15"/>
-      <c r="V2" s="15"/>
-      <c r="W2" s="15"/>
-      <c r="X2" s="15"/>
-      <c r="Y2" s="15"/>
-      <c r="Z2" s="15"/>
-      <c r="AA2" s="15"/>
-      <c r="AB2" s="15"/>
-      <c r="AC2" s="15"/>
-      <c r="AD2" s="15"/>
-      <c r="AE2" s="15"/>
-      <c r="AF2" s="15"/>
-      <c r="AG2" s="15"/>
-      <c r="AH2" s="15"/>
-      <c r="AI2" s="15"/>
-      <c r="AJ2" s="15"/>
-      <c r="AK2" s="15"/>
-      <c r="AL2" s="15"/>
-      <c r="AM2" s="15"/>
-      <c r="AN2" s="15"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16"/>
+      <c r="N2" s="16"/>
+      <c r="O2" s="16"/>
+      <c r="P2" s="16"/>
+      <c r="Q2" s="16"/>
+      <c r="R2" s="16"/>
+      <c r="S2" s="16"/>
+      <c r="T2" s="16"/>
+      <c r="U2" s="16"/>
+      <c r="V2" s="16"/>
+      <c r="W2" s="16"/>
+      <c r="X2" s="16"/>
+      <c r="Y2" s="16"/>
+      <c r="Z2" s="16"/>
+      <c r="AA2" s="16"/>
+      <c r="AB2" s="16"/>
+      <c r="AC2" s="16"/>
+      <c r="AD2" s="16"/>
+      <c r="AE2" s="16"/>
+      <c r="AF2" s="16"/>
+      <c r="AG2" s="16"/>
+      <c r="AH2" s="16"/>
+      <c r="AI2" s="16"/>
+      <c r="AJ2" s="16"/>
+      <c r="AK2" s="16"/>
+      <c r="AL2" s="16"/>
+      <c r="AM2" s="16"/>
+      <c r="AN2" s="16"/>
     </row>
     <row r="3" spans="1:40" ht="13">
       <c r="A3" s="3" t="s">
@@ -9213,7 +9211,6 @@
       <c r="AG16" s="6"/>
     </row>
   </sheetData>
-  <sheetCalcPr fullCalcOnLoad="1"/>
   <mergeCells count="2">
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="A2:AN2"/>

--- a/financial/src/main/resources/template/salary.xlsx
+++ b/financial/src/main/resources/template/salary.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="47">
   <si>
     <t>工资表--1月</t>
   </si>
@@ -182,10 +182,6 @@
      2.工资模板导入时只支持第一个sheet数据导入，导入某月份的工资表时，需要将该月份工资表的sheet移动到第一个sheet位置</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
-  <si>
-    <t>应发工资</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
 </sst>
 </file>
 
@@ -211,13 +207,11 @@
       <b/>
       <sz val="10"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -229,7 +223,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -238,7 +231,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -337,14 +329,14 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -707,64 +699,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:33" ht="47" customHeight="1">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
-      <c r="O1" s="15"/>
-      <c r="P1" s="15"/>
-      <c r="Q1" s="15"/>
-      <c r="R1" s="15"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
+      <c r="O1" s="14"/>
+      <c r="P1" s="14"/>
+      <c r="Q1" s="14"/>
+      <c r="R1" s="14"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:33" s="1" customFormat="1" ht="21" customHeight="1">
-      <c r="A2" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="16"/>
-      <c r="N2" s="16"/>
-      <c r="O2" s="16"/>
-      <c r="P2" s="16"/>
-      <c r="Q2" s="16"/>
-      <c r="R2" s="16"/>
-      <c r="S2" s="16"/>
-      <c r="T2" s="16"/>
-      <c r="U2" s="16"/>
-      <c r="V2" s="16"/>
-      <c r="W2" s="16"/>
-      <c r="X2" s="16"/>
-      <c r="Y2" s="16"/>
-      <c r="Z2" s="16"/>
-      <c r="AA2" s="16"/>
-      <c r="AB2" s="16"/>
-      <c r="AC2" s="16"/>
-      <c r="AD2" s="16"/>
-      <c r="AE2" s="16"/>
-      <c r="AF2" s="16"/>
-      <c r="AG2" s="16"/>
+      <c r="A2" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="15"/>
+      <c r="O2" s="15"/>
+      <c r="P2" s="15"/>
+      <c r="Q2" s="15"/>
+      <c r="R2" s="15"/>
+      <c r="S2" s="15"/>
+      <c r="T2" s="15"/>
+      <c r="U2" s="15"/>
+      <c r="V2" s="15"/>
+      <c r="W2" s="15"/>
+      <c r="X2" s="15"/>
+      <c r="Y2" s="15"/>
+      <c r="Z2" s="15"/>
+      <c r="AA2" s="15"/>
+      <c r="AB2" s="15"/>
+      <c r="AC2" s="15"/>
+      <c r="AD2" s="15"/>
+      <c r="AE2" s="15"/>
+      <c r="AF2" s="15"/>
+      <c r="AG2" s="15"/>
     </row>
     <row r="3" spans="1:33" ht="13">
       <c r="A3" s="3" t="s">
@@ -1409,70 +1401,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" ht="47" customHeight="1">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
-      <c r="O1" s="15"/>
-      <c r="P1" s="15"/>
-      <c r="Q1" s="15"/>
-      <c r="R1" s="15"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
+      <c r="O1" s="14"/>
+      <c r="P1" s="14"/>
+      <c r="Q1" s="14"/>
+      <c r="R1" s="14"/>
     </row>
     <row r="2" spans="1:40" s="1" customFormat="1" ht="21" customHeight="1">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="16"/>
-      <c r="N2" s="16"/>
-      <c r="O2" s="16"/>
-      <c r="P2" s="16"/>
-      <c r="Q2" s="16"/>
-      <c r="R2" s="16"/>
-      <c r="S2" s="16"/>
-      <c r="T2" s="16"/>
-      <c r="U2" s="16"/>
-      <c r="V2" s="16"/>
-      <c r="W2" s="16"/>
-      <c r="X2" s="16"/>
-      <c r="Y2" s="16"/>
-      <c r="Z2" s="16"/>
-      <c r="AA2" s="16"/>
-      <c r="AB2" s="16"/>
-      <c r="AC2" s="16"/>
-      <c r="AD2" s="16"/>
-      <c r="AE2" s="16"/>
-      <c r="AF2" s="16"/>
-      <c r="AG2" s="16"/>
-      <c r="AH2" s="16"/>
-      <c r="AI2" s="16"/>
-      <c r="AJ2" s="16"/>
-      <c r="AK2" s="16"/>
-      <c r="AL2" s="16"/>
-      <c r="AM2" s="16"/>
-      <c r="AN2" s="16"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="15"/>
+      <c r="O2" s="15"/>
+      <c r="P2" s="15"/>
+      <c r="Q2" s="15"/>
+      <c r="R2" s="15"/>
+      <c r="S2" s="15"/>
+      <c r="T2" s="15"/>
+      <c r="U2" s="15"/>
+      <c r="V2" s="15"/>
+      <c r="W2" s="15"/>
+      <c r="X2" s="15"/>
+      <c r="Y2" s="15"/>
+      <c r="Z2" s="15"/>
+      <c r="AA2" s="15"/>
+      <c r="AB2" s="15"/>
+      <c r="AC2" s="15"/>
+      <c r="AD2" s="15"/>
+      <c r="AE2" s="15"/>
+      <c r="AF2" s="15"/>
+      <c r="AG2" s="15"/>
+      <c r="AH2" s="15"/>
+      <c r="AI2" s="15"/>
+      <c r="AJ2" s="15"/>
+      <c r="AK2" s="15"/>
+      <c r="AL2" s="15"/>
+      <c r="AM2" s="15"/>
+      <c r="AN2" s="15"/>
     </row>
     <row r="3" spans="1:40" ht="13">
       <c r="A3" s="3" t="s">
@@ -2081,6 +2073,7 @@
       <c r="AG16" s="6"/>
     </row>
   </sheetData>
+  <sheetCalcPr fullCalcOnLoad="1"/>
   <mergeCells count="2">
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="A2:AN2"/>
@@ -2116,70 +2109,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" ht="47" customHeight="1">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
-      <c r="O1" s="15"/>
-      <c r="P1" s="15"/>
-      <c r="Q1" s="15"/>
-      <c r="R1" s="15"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
+      <c r="O1" s="14"/>
+      <c r="P1" s="14"/>
+      <c r="Q1" s="14"/>
+      <c r="R1" s="14"/>
     </row>
     <row r="2" spans="1:40" s="1" customFormat="1" ht="21" customHeight="1">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="16"/>
-      <c r="N2" s="16"/>
-      <c r="O2" s="16"/>
-      <c r="P2" s="16"/>
-      <c r="Q2" s="16"/>
-      <c r="R2" s="16"/>
-      <c r="S2" s="16"/>
-      <c r="T2" s="16"/>
-      <c r="U2" s="16"/>
-      <c r="V2" s="16"/>
-      <c r="W2" s="16"/>
-      <c r="X2" s="16"/>
-      <c r="Y2" s="16"/>
-      <c r="Z2" s="16"/>
-      <c r="AA2" s="16"/>
-      <c r="AB2" s="16"/>
-      <c r="AC2" s="16"/>
-      <c r="AD2" s="16"/>
-      <c r="AE2" s="16"/>
-      <c r="AF2" s="16"/>
-      <c r="AG2" s="16"/>
-      <c r="AH2" s="16"/>
-      <c r="AI2" s="16"/>
-      <c r="AJ2" s="16"/>
-      <c r="AK2" s="16"/>
-      <c r="AL2" s="16"/>
-      <c r="AM2" s="16"/>
-      <c r="AN2" s="16"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="15"/>
+      <c r="O2" s="15"/>
+      <c r="P2" s="15"/>
+      <c r="Q2" s="15"/>
+      <c r="R2" s="15"/>
+      <c r="S2" s="15"/>
+      <c r="T2" s="15"/>
+      <c r="U2" s="15"/>
+      <c r="V2" s="15"/>
+      <c r="W2" s="15"/>
+      <c r="X2" s="15"/>
+      <c r="Y2" s="15"/>
+      <c r="Z2" s="15"/>
+      <c r="AA2" s="15"/>
+      <c r="AB2" s="15"/>
+      <c r="AC2" s="15"/>
+      <c r="AD2" s="15"/>
+      <c r="AE2" s="15"/>
+      <c r="AF2" s="15"/>
+      <c r="AG2" s="15"/>
+      <c r="AH2" s="15"/>
+      <c r="AI2" s="15"/>
+      <c r="AJ2" s="15"/>
+      <c r="AK2" s="15"/>
+      <c r="AL2" s="15"/>
+      <c r="AM2" s="15"/>
+      <c r="AN2" s="15"/>
     </row>
     <row r="3" spans="1:40" ht="13">
       <c r="A3" s="3" t="s">
@@ -2788,6 +2781,7 @@
       <c r="AG16" s="6"/>
     </row>
   </sheetData>
+  <sheetCalcPr fullCalcOnLoad="1"/>
   <mergeCells count="2">
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="A2:AN2"/>
@@ -2822,70 +2816,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" ht="47" customHeight="1">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
-      <c r="O1" s="15"/>
-      <c r="P1" s="15"/>
-      <c r="Q1" s="15"/>
-      <c r="R1" s="15"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
+      <c r="O1" s="14"/>
+      <c r="P1" s="14"/>
+      <c r="Q1" s="14"/>
+      <c r="R1" s="14"/>
     </row>
     <row r="2" spans="1:40" s="1" customFormat="1" ht="21" customHeight="1">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="16"/>
-      <c r="N2" s="16"/>
-      <c r="O2" s="16"/>
-      <c r="P2" s="16"/>
-      <c r="Q2" s="16"/>
-      <c r="R2" s="16"/>
-      <c r="S2" s="16"/>
-      <c r="T2" s="16"/>
-      <c r="U2" s="16"/>
-      <c r="V2" s="16"/>
-      <c r="W2" s="16"/>
-      <c r="X2" s="16"/>
-      <c r="Y2" s="16"/>
-      <c r="Z2" s="16"/>
-      <c r="AA2" s="16"/>
-      <c r="AB2" s="16"/>
-      <c r="AC2" s="16"/>
-      <c r="AD2" s="16"/>
-      <c r="AE2" s="16"/>
-      <c r="AF2" s="16"/>
-      <c r="AG2" s="16"/>
-      <c r="AH2" s="16"/>
-      <c r="AI2" s="16"/>
-      <c r="AJ2" s="16"/>
-      <c r="AK2" s="16"/>
-      <c r="AL2" s="16"/>
-      <c r="AM2" s="16"/>
-      <c r="AN2" s="16"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="15"/>
+      <c r="O2" s="15"/>
+      <c r="P2" s="15"/>
+      <c r="Q2" s="15"/>
+      <c r="R2" s="15"/>
+      <c r="S2" s="15"/>
+      <c r="T2" s="15"/>
+      <c r="U2" s="15"/>
+      <c r="V2" s="15"/>
+      <c r="W2" s="15"/>
+      <c r="X2" s="15"/>
+      <c r="Y2" s="15"/>
+      <c r="Z2" s="15"/>
+      <c r="AA2" s="15"/>
+      <c r="AB2" s="15"/>
+      <c r="AC2" s="15"/>
+      <c r="AD2" s="15"/>
+      <c r="AE2" s="15"/>
+      <c r="AF2" s="15"/>
+      <c r="AG2" s="15"/>
+      <c r="AH2" s="15"/>
+      <c r="AI2" s="15"/>
+      <c r="AJ2" s="15"/>
+      <c r="AK2" s="15"/>
+      <c r="AL2" s="15"/>
+      <c r="AM2" s="15"/>
+      <c r="AN2" s="15"/>
     </row>
     <row r="3" spans="1:40" ht="13">
       <c r="A3" s="3" t="s">
@@ -2928,7 +2922,7 @@
         <v>13</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="O3" s="3" t="s">
         <v>15</v>
@@ -3542,6 +3536,7 @@
       <c r="O34" s="12"/>
     </row>
   </sheetData>
+  <sheetCalcPr fullCalcOnLoad="1"/>
   <mergeCells count="2">
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="A2:AN2"/>
@@ -3584,63 +3579,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:33" ht="47" customHeight="1">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
-      <c r="O1" s="15"/>
-      <c r="P1" s="15"/>
-      <c r="Q1" s="15"/>
-      <c r="R1" s="15"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
+      <c r="O1" s="14"/>
+      <c r="P1" s="14"/>
+      <c r="Q1" s="14"/>
+      <c r="R1" s="14"/>
     </row>
     <row r="2" spans="1:33" s="1" customFormat="1" ht="21" customHeight="1">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="16"/>
-      <c r="N2" s="16"/>
-      <c r="O2" s="16"/>
-      <c r="P2" s="16"/>
-      <c r="Q2" s="16"/>
-      <c r="R2" s="16"/>
-      <c r="S2" s="16"/>
-      <c r="T2" s="16"/>
-      <c r="U2" s="16"/>
-      <c r="V2" s="16"/>
-      <c r="W2" s="16"/>
-      <c r="X2" s="16"/>
-      <c r="Y2" s="16"/>
-      <c r="Z2" s="16"/>
-      <c r="AA2" s="16"/>
-      <c r="AB2" s="16"/>
-      <c r="AC2" s="16"/>
-      <c r="AD2" s="16"/>
-      <c r="AE2" s="16"/>
-      <c r="AF2" s="16"/>
-      <c r="AG2" s="16"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="15"/>
+      <c r="O2" s="15"/>
+      <c r="P2" s="15"/>
+      <c r="Q2" s="15"/>
+      <c r="R2" s="15"/>
+      <c r="S2" s="15"/>
+      <c r="T2" s="15"/>
+      <c r="U2" s="15"/>
+      <c r="V2" s="15"/>
+      <c r="W2" s="15"/>
+      <c r="X2" s="15"/>
+      <c r="Y2" s="15"/>
+      <c r="Z2" s="15"/>
+      <c r="AA2" s="15"/>
+      <c r="AB2" s="15"/>
+      <c r="AC2" s="15"/>
+      <c r="AD2" s="15"/>
+      <c r="AE2" s="15"/>
+      <c r="AF2" s="15"/>
+      <c r="AG2" s="15"/>
     </row>
     <row r="3" spans="1:33" ht="13">
       <c r="A3" s="3" t="s">
@@ -4249,6 +4244,7 @@
       <c r="AG16" s="6"/>
     </row>
   </sheetData>
+  <sheetCalcPr fullCalcOnLoad="1"/>
   <mergeCells count="2">
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="A2:AG2"/>
@@ -4291,70 +4287,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" ht="47" customHeight="1">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
-      <c r="O1" s="15"/>
-      <c r="P1" s="15"/>
-      <c r="Q1" s="15"/>
-      <c r="R1" s="15"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
+      <c r="O1" s="14"/>
+      <c r="P1" s="14"/>
+      <c r="Q1" s="14"/>
+      <c r="R1" s="14"/>
     </row>
     <row r="2" spans="1:40" s="1" customFormat="1" ht="21" customHeight="1">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="16"/>
-      <c r="N2" s="16"/>
-      <c r="O2" s="16"/>
-      <c r="P2" s="16"/>
-      <c r="Q2" s="16"/>
-      <c r="R2" s="16"/>
-      <c r="S2" s="16"/>
-      <c r="T2" s="16"/>
-      <c r="U2" s="16"/>
-      <c r="V2" s="16"/>
-      <c r="W2" s="16"/>
-      <c r="X2" s="16"/>
-      <c r="Y2" s="16"/>
-      <c r="Z2" s="16"/>
-      <c r="AA2" s="16"/>
-      <c r="AB2" s="16"/>
-      <c r="AC2" s="16"/>
-      <c r="AD2" s="16"/>
-      <c r="AE2" s="16"/>
-      <c r="AF2" s="16"/>
-      <c r="AG2" s="16"/>
-      <c r="AH2" s="16"/>
-      <c r="AI2" s="16"/>
-      <c r="AJ2" s="16"/>
-      <c r="AK2" s="16"/>
-      <c r="AL2" s="16"/>
-      <c r="AM2" s="16"/>
-      <c r="AN2" s="16"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="15"/>
+      <c r="O2" s="15"/>
+      <c r="P2" s="15"/>
+      <c r="Q2" s="15"/>
+      <c r="R2" s="15"/>
+      <c r="S2" s="15"/>
+      <c r="T2" s="15"/>
+      <c r="U2" s="15"/>
+      <c r="V2" s="15"/>
+      <c r="W2" s="15"/>
+      <c r="X2" s="15"/>
+      <c r="Y2" s="15"/>
+      <c r="Z2" s="15"/>
+      <c r="AA2" s="15"/>
+      <c r="AB2" s="15"/>
+      <c r="AC2" s="15"/>
+      <c r="AD2" s="15"/>
+      <c r="AE2" s="15"/>
+      <c r="AF2" s="15"/>
+      <c r="AG2" s="15"/>
+      <c r="AH2" s="15"/>
+      <c r="AI2" s="15"/>
+      <c r="AJ2" s="15"/>
+      <c r="AK2" s="15"/>
+      <c r="AL2" s="15"/>
+      <c r="AM2" s="15"/>
+      <c r="AN2" s="15"/>
     </row>
     <row r="3" spans="1:40" ht="13">
       <c r="A3" s="3" t="s">
@@ -4963,6 +4959,7 @@
       <c r="AG16" s="6"/>
     </row>
   </sheetData>
+  <sheetCalcPr fullCalcOnLoad="1"/>
   <mergeCells count="2">
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="A2:AN2"/>
@@ -5005,70 +5002,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" ht="47" customHeight="1">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
-      <c r="O1" s="15"/>
-      <c r="P1" s="15"/>
-      <c r="Q1" s="15"/>
-      <c r="R1" s="15"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
+      <c r="O1" s="14"/>
+      <c r="P1" s="14"/>
+      <c r="Q1" s="14"/>
+      <c r="R1" s="14"/>
     </row>
     <row r="2" spans="1:40" s="1" customFormat="1" ht="21" customHeight="1">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="16"/>
-      <c r="N2" s="16"/>
-      <c r="O2" s="16"/>
-      <c r="P2" s="16"/>
-      <c r="Q2" s="16"/>
-      <c r="R2" s="16"/>
-      <c r="S2" s="16"/>
-      <c r="T2" s="16"/>
-      <c r="U2" s="16"/>
-      <c r="V2" s="16"/>
-      <c r="W2" s="16"/>
-      <c r="X2" s="16"/>
-      <c r="Y2" s="16"/>
-      <c r="Z2" s="16"/>
-      <c r="AA2" s="16"/>
-      <c r="AB2" s="16"/>
-      <c r="AC2" s="16"/>
-      <c r="AD2" s="16"/>
-      <c r="AE2" s="16"/>
-      <c r="AF2" s="16"/>
-      <c r="AG2" s="16"/>
-      <c r="AH2" s="16"/>
-      <c r="AI2" s="16"/>
-      <c r="AJ2" s="16"/>
-      <c r="AK2" s="16"/>
-      <c r="AL2" s="16"/>
-      <c r="AM2" s="16"/>
-      <c r="AN2" s="16"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="15"/>
+      <c r="O2" s="15"/>
+      <c r="P2" s="15"/>
+      <c r="Q2" s="15"/>
+      <c r="R2" s="15"/>
+      <c r="S2" s="15"/>
+      <c r="T2" s="15"/>
+      <c r="U2" s="15"/>
+      <c r="V2" s="15"/>
+      <c r="W2" s="15"/>
+      <c r="X2" s="15"/>
+      <c r="Y2" s="15"/>
+      <c r="Z2" s="15"/>
+      <c r="AA2" s="15"/>
+      <c r="AB2" s="15"/>
+      <c r="AC2" s="15"/>
+      <c r="AD2" s="15"/>
+      <c r="AE2" s="15"/>
+      <c r="AF2" s="15"/>
+      <c r="AG2" s="15"/>
+      <c r="AH2" s="15"/>
+      <c r="AI2" s="15"/>
+      <c r="AJ2" s="15"/>
+      <c r="AK2" s="15"/>
+      <c r="AL2" s="15"/>
+      <c r="AM2" s="15"/>
+      <c r="AN2" s="15"/>
     </row>
     <row r="3" spans="1:40" ht="13">
       <c r="A3" s="3" t="s">
@@ -5677,6 +5674,7 @@
       <c r="AG16" s="6"/>
     </row>
   </sheetData>
+  <sheetCalcPr fullCalcOnLoad="1"/>
   <mergeCells count="2">
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="A2:AN2"/>
@@ -5710,70 +5708,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" ht="47" customHeight="1">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
-      <c r="O1" s="15"/>
-      <c r="P1" s="15"/>
-      <c r="Q1" s="15"/>
-      <c r="R1" s="15"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
+      <c r="O1" s="14"/>
+      <c r="P1" s="14"/>
+      <c r="Q1" s="14"/>
+      <c r="R1" s="14"/>
     </row>
     <row r="2" spans="1:40" s="1" customFormat="1" ht="21" customHeight="1">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="16"/>
-      <c r="N2" s="16"/>
-      <c r="O2" s="16"/>
-      <c r="P2" s="16"/>
-      <c r="Q2" s="16"/>
-      <c r="R2" s="16"/>
-      <c r="S2" s="16"/>
-      <c r="T2" s="16"/>
-      <c r="U2" s="16"/>
-      <c r="V2" s="16"/>
-      <c r="W2" s="16"/>
-      <c r="X2" s="16"/>
-      <c r="Y2" s="16"/>
-      <c r="Z2" s="16"/>
-      <c r="AA2" s="16"/>
-      <c r="AB2" s="16"/>
-      <c r="AC2" s="16"/>
-      <c r="AD2" s="16"/>
-      <c r="AE2" s="16"/>
-      <c r="AF2" s="16"/>
-      <c r="AG2" s="16"/>
-      <c r="AH2" s="16"/>
-      <c r="AI2" s="16"/>
-      <c r="AJ2" s="16"/>
-      <c r="AK2" s="16"/>
-      <c r="AL2" s="16"/>
-      <c r="AM2" s="16"/>
-      <c r="AN2" s="16"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="15"/>
+      <c r="O2" s="15"/>
+      <c r="P2" s="15"/>
+      <c r="Q2" s="15"/>
+      <c r="R2" s="15"/>
+      <c r="S2" s="15"/>
+      <c r="T2" s="15"/>
+      <c r="U2" s="15"/>
+      <c r="V2" s="15"/>
+      <c r="W2" s="15"/>
+      <c r="X2" s="15"/>
+      <c r="Y2" s="15"/>
+      <c r="Z2" s="15"/>
+      <c r="AA2" s="15"/>
+      <c r="AB2" s="15"/>
+      <c r="AC2" s="15"/>
+      <c r="AD2" s="15"/>
+      <c r="AE2" s="15"/>
+      <c r="AF2" s="15"/>
+      <c r="AG2" s="15"/>
+      <c r="AH2" s="15"/>
+      <c r="AI2" s="15"/>
+      <c r="AJ2" s="15"/>
+      <c r="AK2" s="15"/>
+      <c r="AL2" s="15"/>
+      <c r="AM2" s="15"/>
+      <c r="AN2" s="15"/>
     </row>
     <row r="3" spans="1:40" ht="13">
       <c r="A3" s="3" t="s">
@@ -6382,6 +6380,7 @@
       <c r="AG16" s="6"/>
     </row>
   </sheetData>
+  <sheetCalcPr fullCalcOnLoad="1"/>
   <mergeCells count="2">
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="A2:AN2"/>
@@ -6415,70 +6414,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" ht="47" customHeight="1">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
-      <c r="O1" s="15"/>
-      <c r="P1" s="15"/>
-      <c r="Q1" s="15"/>
-      <c r="R1" s="15"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
+      <c r="O1" s="14"/>
+      <c r="P1" s="14"/>
+      <c r="Q1" s="14"/>
+      <c r="R1" s="14"/>
     </row>
     <row r="2" spans="1:40" s="1" customFormat="1" ht="21" customHeight="1">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="16"/>
-      <c r="N2" s="16"/>
-      <c r="O2" s="16"/>
-      <c r="P2" s="16"/>
-      <c r="Q2" s="16"/>
-      <c r="R2" s="16"/>
-      <c r="S2" s="16"/>
-      <c r="T2" s="16"/>
-      <c r="U2" s="16"/>
-      <c r="V2" s="16"/>
-      <c r="W2" s="16"/>
-      <c r="X2" s="16"/>
-      <c r="Y2" s="16"/>
-      <c r="Z2" s="16"/>
-      <c r="AA2" s="16"/>
-      <c r="AB2" s="16"/>
-      <c r="AC2" s="16"/>
-      <c r="AD2" s="16"/>
-      <c r="AE2" s="16"/>
-      <c r="AF2" s="16"/>
-      <c r="AG2" s="16"/>
-      <c r="AH2" s="16"/>
-      <c r="AI2" s="16"/>
-      <c r="AJ2" s="16"/>
-      <c r="AK2" s="16"/>
-      <c r="AL2" s="16"/>
-      <c r="AM2" s="16"/>
-      <c r="AN2" s="16"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="15"/>
+      <c r="O2" s="15"/>
+      <c r="P2" s="15"/>
+      <c r="Q2" s="15"/>
+      <c r="R2" s="15"/>
+      <c r="S2" s="15"/>
+      <c r="T2" s="15"/>
+      <c r="U2" s="15"/>
+      <c r="V2" s="15"/>
+      <c r="W2" s="15"/>
+      <c r="X2" s="15"/>
+      <c r="Y2" s="15"/>
+      <c r="Z2" s="15"/>
+      <c r="AA2" s="15"/>
+      <c r="AB2" s="15"/>
+      <c r="AC2" s="15"/>
+      <c r="AD2" s="15"/>
+      <c r="AE2" s="15"/>
+      <c r="AF2" s="15"/>
+      <c r="AG2" s="15"/>
+      <c r="AH2" s="15"/>
+      <c r="AI2" s="15"/>
+      <c r="AJ2" s="15"/>
+      <c r="AK2" s="15"/>
+      <c r="AL2" s="15"/>
+      <c r="AM2" s="15"/>
+      <c r="AN2" s="15"/>
     </row>
     <row r="3" spans="1:40" ht="13">
       <c r="A3" s="3" t="s">
@@ -7087,6 +7086,7 @@
       <c r="AG16" s="6"/>
     </row>
   </sheetData>
+  <sheetCalcPr fullCalcOnLoad="1"/>
   <mergeCells count="2">
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="A2:AN2"/>
@@ -7123,70 +7123,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" ht="47" customHeight="1">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
-      <c r="O1" s="15"/>
-      <c r="P1" s="15"/>
-      <c r="Q1" s="15"/>
-      <c r="R1" s="15"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
+      <c r="O1" s="14"/>
+      <c r="P1" s="14"/>
+      <c r="Q1" s="14"/>
+      <c r="R1" s="14"/>
     </row>
     <row r="2" spans="1:40" s="1" customFormat="1" ht="21" customHeight="1">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="16"/>
-      <c r="N2" s="16"/>
-      <c r="O2" s="16"/>
-      <c r="P2" s="16"/>
-      <c r="Q2" s="16"/>
-      <c r="R2" s="16"/>
-      <c r="S2" s="16"/>
-      <c r="T2" s="16"/>
-      <c r="U2" s="16"/>
-      <c r="V2" s="16"/>
-      <c r="W2" s="16"/>
-      <c r="X2" s="16"/>
-      <c r="Y2" s="16"/>
-      <c r="Z2" s="16"/>
-      <c r="AA2" s="16"/>
-      <c r="AB2" s="16"/>
-      <c r="AC2" s="16"/>
-      <c r="AD2" s="16"/>
-      <c r="AE2" s="16"/>
-      <c r="AF2" s="16"/>
-      <c r="AG2" s="16"/>
-      <c r="AH2" s="16"/>
-      <c r="AI2" s="16"/>
-      <c r="AJ2" s="16"/>
-      <c r="AK2" s="16"/>
-      <c r="AL2" s="16"/>
-      <c r="AM2" s="16"/>
-      <c r="AN2" s="16"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="15"/>
+      <c r="O2" s="15"/>
+      <c r="P2" s="15"/>
+      <c r="Q2" s="15"/>
+      <c r="R2" s="15"/>
+      <c r="S2" s="15"/>
+      <c r="T2" s="15"/>
+      <c r="U2" s="15"/>
+      <c r="V2" s="15"/>
+      <c r="W2" s="15"/>
+      <c r="X2" s="15"/>
+      <c r="Y2" s="15"/>
+      <c r="Z2" s="15"/>
+      <c r="AA2" s="15"/>
+      <c r="AB2" s="15"/>
+      <c r="AC2" s="15"/>
+      <c r="AD2" s="15"/>
+      <c r="AE2" s="15"/>
+      <c r="AF2" s="15"/>
+      <c r="AG2" s="15"/>
+      <c r="AH2" s="15"/>
+      <c r="AI2" s="15"/>
+      <c r="AJ2" s="15"/>
+      <c r="AK2" s="15"/>
+      <c r="AL2" s="15"/>
+      <c r="AM2" s="15"/>
+      <c r="AN2" s="15"/>
     </row>
     <row r="3" spans="1:40" ht="13">
       <c r="A3" s="3" t="s">
@@ -7795,6 +7795,7 @@
       <c r="AG16" s="6"/>
     </row>
   </sheetData>
+  <sheetCalcPr fullCalcOnLoad="1"/>
   <mergeCells count="2">
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="A2:AN2"/>
@@ -7832,70 +7833,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" ht="47" customHeight="1">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
-      <c r="O1" s="15"/>
-      <c r="P1" s="15"/>
-      <c r="Q1" s="15"/>
-      <c r="R1" s="15"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
+      <c r="O1" s="14"/>
+      <c r="P1" s="14"/>
+      <c r="Q1" s="14"/>
+      <c r="R1" s="14"/>
     </row>
     <row r="2" spans="1:40" s="1" customFormat="1" ht="21" customHeight="1">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="16"/>
-      <c r="N2" s="16"/>
-      <c r="O2" s="16"/>
-      <c r="P2" s="16"/>
-      <c r="Q2" s="16"/>
-      <c r="R2" s="16"/>
-      <c r="S2" s="16"/>
-      <c r="T2" s="16"/>
-      <c r="U2" s="16"/>
-      <c r="V2" s="16"/>
-      <c r="W2" s="16"/>
-      <c r="X2" s="16"/>
-      <c r="Y2" s="16"/>
-      <c r="Z2" s="16"/>
-      <c r="AA2" s="16"/>
-      <c r="AB2" s="16"/>
-      <c r="AC2" s="16"/>
-      <c r="AD2" s="16"/>
-      <c r="AE2" s="16"/>
-      <c r="AF2" s="16"/>
-      <c r="AG2" s="16"/>
-      <c r="AH2" s="16"/>
-      <c r="AI2" s="16"/>
-      <c r="AJ2" s="16"/>
-      <c r="AK2" s="16"/>
-      <c r="AL2" s="16"/>
-      <c r="AM2" s="16"/>
-      <c r="AN2" s="16"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="15"/>
+      <c r="O2" s="15"/>
+      <c r="P2" s="15"/>
+      <c r="Q2" s="15"/>
+      <c r="R2" s="15"/>
+      <c r="S2" s="15"/>
+      <c r="T2" s="15"/>
+      <c r="U2" s="15"/>
+      <c r="V2" s="15"/>
+      <c r="W2" s="15"/>
+      <c r="X2" s="15"/>
+      <c r="Y2" s="15"/>
+      <c r="Z2" s="15"/>
+      <c r="AA2" s="15"/>
+      <c r="AB2" s="15"/>
+      <c r="AC2" s="15"/>
+      <c r="AD2" s="15"/>
+      <c r="AE2" s="15"/>
+      <c r="AF2" s="15"/>
+      <c r="AG2" s="15"/>
+      <c r="AH2" s="15"/>
+      <c r="AI2" s="15"/>
+      <c r="AJ2" s="15"/>
+      <c r="AK2" s="15"/>
+      <c r="AL2" s="15"/>
+      <c r="AM2" s="15"/>
+      <c r="AN2" s="15"/>
     </row>
     <row r="3" spans="1:40" ht="13">
       <c r="A3" s="3" t="s">
@@ -8504,6 +8505,7 @@
       <c r="AG16" s="6"/>
     </row>
   </sheetData>
+  <sheetCalcPr fullCalcOnLoad="1"/>
   <mergeCells count="2">
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="A2:AN2"/>
@@ -8539,70 +8541,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" ht="47" customHeight="1">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
-      <c r="O1" s="15"/>
-      <c r="P1" s="15"/>
-      <c r="Q1" s="15"/>
-      <c r="R1" s="15"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
+      <c r="O1" s="14"/>
+      <c r="P1" s="14"/>
+      <c r="Q1" s="14"/>
+      <c r="R1" s="14"/>
     </row>
     <row r="2" spans="1:40" s="1" customFormat="1" ht="21" customHeight="1">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="16"/>
-      <c r="N2" s="16"/>
-      <c r="O2" s="16"/>
-      <c r="P2" s="16"/>
-      <c r="Q2" s="16"/>
-      <c r="R2" s="16"/>
-      <c r="S2" s="16"/>
-      <c r="T2" s="16"/>
-      <c r="U2" s="16"/>
-      <c r="V2" s="16"/>
-      <c r="W2" s="16"/>
-      <c r="X2" s="16"/>
-      <c r="Y2" s="16"/>
-      <c r="Z2" s="16"/>
-      <c r="AA2" s="16"/>
-      <c r="AB2" s="16"/>
-      <c r="AC2" s="16"/>
-      <c r="AD2" s="16"/>
-      <c r="AE2" s="16"/>
-      <c r="AF2" s="16"/>
-      <c r="AG2" s="16"/>
-      <c r="AH2" s="16"/>
-      <c r="AI2" s="16"/>
-      <c r="AJ2" s="16"/>
-      <c r="AK2" s="16"/>
-      <c r="AL2" s="16"/>
-      <c r="AM2" s="16"/>
-      <c r="AN2" s="16"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="15"/>
+      <c r="O2" s="15"/>
+      <c r="P2" s="15"/>
+      <c r="Q2" s="15"/>
+      <c r="R2" s="15"/>
+      <c r="S2" s="15"/>
+      <c r="T2" s="15"/>
+      <c r="U2" s="15"/>
+      <c r="V2" s="15"/>
+      <c r="W2" s="15"/>
+      <c r="X2" s="15"/>
+      <c r="Y2" s="15"/>
+      <c r="Z2" s="15"/>
+      <c r="AA2" s="15"/>
+      <c r="AB2" s="15"/>
+      <c r="AC2" s="15"/>
+      <c r="AD2" s="15"/>
+      <c r="AE2" s="15"/>
+      <c r="AF2" s="15"/>
+      <c r="AG2" s="15"/>
+      <c r="AH2" s="15"/>
+      <c r="AI2" s="15"/>
+      <c r="AJ2" s="15"/>
+      <c r="AK2" s="15"/>
+      <c r="AL2" s="15"/>
+      <c r="AM2" s="15"/>
+      <c r="AN2" s="15"/>
     </row>
     <row r="3" spans="1:40" ht="13">
       <c r="A3" s="3" t="s">
@@ -9211,6 +9213,7 @@
       <c r="AG16" s="6"/>
     </row>
   </sheetData>
+  <sheetCalcPr fullCalcOnLoad="1"/>
   <mergeCells count="2">
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="A2:AN2"/>
